--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{06F6B68C-98DB-4A01-A3E6-89E0F1AF4360}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{8A34E824-18E2-44C1-972F-C712BCA2976E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="24" firstSheet="22" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView activeTab="5" firstSheet="5" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="CVCSPSCFCorp_IPDailyNOP" r:id="rId1" sheetId="1"/>
@@ -134,292 +134,10 @@
     <t>Deferred</t>
   </si>
   <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Savings,3. Payment Plan Information,
-Payment Plan Type:,	Automatic Payment 
-Payment Plan Start Date:,	
-4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,3. Payment Plan Information,
-Payment Plan Type:,	Automatic Payment 
-Payment Plan Start Date:,	
-4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Savings,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Savings,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Savings,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
     <t>IndividualAmount</t>
   </si>
   <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Savings,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $</t>
-  </si>
-  <si>
-    <t>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
-1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $</t>
-  </si>
-  <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:19:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:20:55 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:22:08 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:23:41 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:25:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:26:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:28:06 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:29:32 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:30:43 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:32:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:34:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:35:30 IST 2025</t>
   </si>
   <si>
     <t>Fri Dec 26 21:37:24 IST 2025</t>
@@ -739,10 +457,293 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
+    <t>Sun Jan 04 23:39:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+Company Name:,	Vaddahun Corp,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Business Checking,
+Account Type:,	Personal Checking,3. Payment Plan Information,
+Payment Plan Type:,	Automatic Payment 
+Payment Plan Start Date:,	
+4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 19:40:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Installment Plan,
+Payment Plan Duration:,	Daily,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Daily payment of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 20:35:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 20:44:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Installment Plan,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 21:24:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Daily,
+Payment Plan Start Date:,	
+4. Payment Plan, Daily payments of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 21:29:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Checking,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 21:33:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Savings,3. Payment Plan Information,
+Payment Plan Type:,	Automatic Payment 
+Payment Plan Start Date:,	
+4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 22:45:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Savings,
+3. Payment Plan Information,
+Payment Plan Type:,	Installment Plan,
+Payment Plan Duration:,	Daily,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Daily payment of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 22:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 23:03:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Savings,
+3. Payment Plan Information,
+Payment Plan Type:,	Installment Plan,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 23:08:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Account Type:,	Personal Savings,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Daily,
+Payment Plan Start Date:,	
+4. Payment Plan, Daily payments of $</t>
+  </si>
+  <si>
+    <t>Tue Jan 06 23:12:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,
+Remittance ID: 6210-402999,
+1. Review bill to pay,
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
+UDF1:,	udf data 1,
+UDF2:,	udf data 2,
+UDF3:,	udf3,
+UDF4:,	udf data4,
+2. Payment Method,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
+Country:,	UNITED STATES,
+Account Type:,	Personal Savings,
+3. Payment Plan Information,
+Payment Plan Type:,	Recurring,
+Payment Plan Duration:,	Deferred,
+Payment Plan Start Date:,	
+4. Payment Plan,1 Deferred payment of $</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Sun Jan 04 23:39:54 IST 2026</t>
+    <t>Tue Jan 06 23:16:45 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1213,11 +1214,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1251,7 +1252,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1259,7 +1260,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1335,7 +1336,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1361,11 +1362,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1376,28 +1377,27 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
-Country:,	UNITED STATES,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Account Type:,	Personal Savings,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1405,7 +1405,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1504,11 +1504,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1519,28 +1519,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
 Routing Number:,	****2691,
 Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1548,7 +1548,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1647,11 +1647,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1685,7 +1685,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1693,7 +1693,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1792,11 +1792,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1827,7 +1827,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1835,7 +1835,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1936,11 +1936,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1951,28 +1951,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Savings,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1980,7 +1980,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2079,11 +2079,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2094,28 +2094,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
 Routing Number:,	****2691,
 Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2123,7 +2123,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2222,11 +2222,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2257,7 +2257,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2265,7 +2265,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2364,11 +2364,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2402,7 +2402,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2410,7 +2410,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2506,14 +2506,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2524,28 +2524,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Savings,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2553,7 +2553,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2649,14 +2649,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2667,28 +2667,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
 Routing Number:,	****2691,
 Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2696,7 +2696,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2795,11 +2795,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2885,7 +2885,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2908,14 +2908,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2946,7 +2946,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2954,7 +2954,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3050,14 +3050,14 @@
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3091,7 +3091,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3099,7 +3099,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3198,11 +3198,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3233,7 +3233,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3241,7 +3241,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3340,11 +3340,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3355,28 +3355,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
 Routing Number:,	****2691,
 Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3384,7 +3384,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3483,11 +3483,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3498,28 +3498,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Savings,
 3. Payment Plan Information,
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3527,7 +3527,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3620,17 +3620,17 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3664,7 +3664,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Monthly,
 Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/05/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,Monthly payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3672,7 +3672,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3774,11 +3774,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3864,7 +3864,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3890,11 +3890,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3980,7 +3980,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4006,11 +4006,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4096,7 +4096,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4122,11 +4122,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4137,28 +4137,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
-Routing Number:,	****4974,
-Account Number:,	****7002,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
+Routing Number:,	****2691,
+Account Number:,	****5489,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Savings,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4166,7 +4166,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4265,11 +4265,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4280,28 +4280,28 @@
       <c r="O2" s="9" t="str">
         <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
         <v>Scheduled Payment--View the Information,
-180RemittanceID: 917-152027,
+Remittance ID: 6210-402999,
 1. Review bill to pay,
-Bills Label,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,
-ImtiazABPsingleCFBills,	 EST, 	
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
+AutoABPDemoBBGSCF6210,	 EST, 	
 UDF1:,	udf data 1,
 UDF2:,	udf data 2,
 UDF3:,	udf3,
 UDF4:,	udf data4,
 2. Payment Method,
-First Name:,	CAROLYN,
-Last Name:,	LINEBERGER,
+First Name:,	DULIP,
+Last Name:,	EKANAYAKE,
 Routing Number:,	****2691,
 Account Number:,	****5489,
-Billing Address:,	7072 MAPLE GLEN DR,
-CATAWBA, North Carolina NC 28609,
+Billing Address:,	708 36TH AVE NW,,
+Hickory, New York NY, 28601,
 Country:,	UNITED STATES,
 Account Type:,	Personal Checking,
 3. Payment Plan Information,
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4309,7 +4309,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4408,11 +4408,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4446,7 +4446,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4454,7 +4454,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4553,11 +4553,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/05/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4588,7 +4588,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/05/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4596,7 +4596,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/05/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>

--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="138">
   <si>
     <t>Result</t>
   </si>
@@ -744,6 +744,198 @@
   </si>
   <si>
     <t>Tue Jan 06 23:16:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:42:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:43:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:45:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:47:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:48:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:50:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:52:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:55:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:58:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 20:59:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:00:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:01:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:02:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:03:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:05:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:06:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:09:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:11:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:13:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:14:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:15:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:16:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:17:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:19:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:21:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:21:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:22:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:24:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:26:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:28:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:30:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:32:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:33:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:34:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:36:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:37:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:38:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:39:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:40:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:41:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:42:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:43:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:46:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:47:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:49:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:50:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:51:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:52:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:53:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 21:53:53 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="23.6328125" collapsed="true"/>
@@ -1155,13 +1347,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1184,11 +1376,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
+      <c r="B2" t="s" s="0">
+        <v>91</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1200,17 +1392,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1275,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="26.08984375" collapsed="true"/>
@@ -1303,13 +1495,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1332,11 +1524,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>70</v>
+      <c r="B2" t="s" s="0">
+        <v>136</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1348,17 +1540,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1417,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.7265625" collapsed="true"/>
@@ -1445,13 +1637,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1474,11 +1666,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
+      <c r="B2" t="s" s="0">
+        <v>127</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1490,17 +1682,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1560,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.7265625" collapsed="true"/>
@@ -1588,13 +1780,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1617,11 +1809,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>46</v>
+      <c r="B2" t="s" s="0">
+        <v>99</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1633,17 +1825,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1705,7 +1897,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="34.7265625" collapsed="true"/>
@@ -1733,13 +1925,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1762,11 +1954,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
+      <c r="B2" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1778,17 +1970,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1847,7 +2039,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.7265625" collapsed="true"/>
@@ -1877,13 +2069,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1906,11 +2098,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>68</v>
+      <c r="B2" t="s" s="0">
+        <v>135</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1922,17 +2114,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1992,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.26953125" collapsed="true"/>
@@ -2020,13 +2212,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2049,11 +2241,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>57</v>
+      <c r="B2" t="s" s="0">
+        <v>123</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2065,17 +2257,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2135,7 +2327,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.7265625" collapsed="true"/>
@@ -2163,13 +2355,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2192,11 +2384,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>77</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2208,17 +2400,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2277,7 +2469,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.81640625" collapsed="true"/>
@@ -2305,13 +2497,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2334,11 +2526,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>44</v>
+      <c r="B2" t="s" s="0">
+        <v>95</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2350,17 +2542,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2422,7 +2614,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.0" collapsed="true"/>
@@ -2450,13 +2642,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2479,11 +2671,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>65</v>
+      <c r="B2" t="s" s="0">
+        <v>133</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2495,17 +2687,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2565,7 +2757,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.08984375" collapsed="true"/>
@@ -2593,13 +2785,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2622,11 +2814,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>54</v>
+      <c r="B2" t="s" s="0">
+        <v>115</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2638,17 +2830,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2708,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.90625" collapsed="true"/>
@@ -2736,13 +2928,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2765,11 +2957,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>39</v>
+      <c r="B2" t="s" s="0">
+        <v>83</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2781,17 +2973,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2824,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
@@ -2852,13 +3044,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2881,11 +3073,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
+      <c r="B2" t="s" s="0">
+        <v>75</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2897,17 +3089,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2966,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.36328125" collapsed="true"/>
@@ -2994,13 +3186,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3023,11 +3215,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>41</v>
+      <c r="B2" t="s" s="0">
+        <v>87</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3039,17 +3231,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3111,7 +3303,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.08984375" collapsed="true"/>
@@ -3139,13 +3331,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3168,11 +3360,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
+      <c r="B2" t="s" s="0">
+        <v>76</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3184,17 +3376,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3253,7 +3445,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.0" collapsed="true"/>
@@ -3281,13 +3473,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3310,11 +3502,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>55</v>
+      <c r="B2" t="s" s="0">
+        <v>119</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3326,17 +3518,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3396,7 +3588,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.90625" collapsed="true"/>
@@ -3424,13 +3616,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3453,11 +3645,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>66</v>
+      <c r="B2" t="s" s="0">
+        <v>134</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3469,17 +3661,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3539,7 +3731,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.1796875" collapsed="true"/>
@@ -3567,13 +3759,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3596,11 +3788,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>50</v>
+      <c r="B2" t="s" s="0">
+        <v>107</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3612,17 +3804,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3684,7 +3876,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
@@ -3715,13 +3907,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3744,11 +3936,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>52</v>
+      <c r="B2" t="s" s="0">
+        <v>111</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3760,17 +3952,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3803,7 +3995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="19.6328125" collapsed="true"/>
@@ -3831,13 +4023,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3860,11 +4052,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>63</v>
+      <c r="B2" t="s" s="0">
+        <v>132</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3876,17 +4068,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -3919,7 +4111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.54296875" collapsed="true"/>
@@ -3947,13 +4139,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -3976,11 +4168,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>28</v>
+      <c r="B2" t="s" s="0">
+        <v>74</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3992,17 +4184,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4035,7 +4227,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="17.90625" collapsed="true"/>
@@ -4063,13 +4255,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4092,11 +4284,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>73</v>
+      <c r="B2" t="s" s="0">
+        <v>137</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4108,17 +4300,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4178,7 +4370,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.81640625" collapsed="true"/>
@@ -4206,13 +4398,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4235,11 +4427,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>61</v>
+      <c r="B2" t="s" s="0">
+        <v>131</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4251,17 +4443,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Carlos"</f>
         <v>Carlos</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4321,7 +4513,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
@@ -4349,13 +4541,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4378,11 +4570,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
+      <c r="B2" t="s" s="0">
+        <v>103</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4394,17 +4586,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -4466,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="28.54296875" collapsed="true"/>
@@ -4494,13 +4686,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -4523,11 +4715,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
+      <c r="B2" t="s" s="0">
+        <v>79</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4539,17 +4731,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">

--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_SCF_Demo.xlsx
@@ -1,43 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8A34E824-18E2-44C1-972F-C712BCA2976E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833B9275-C533-4F9F-88A7-8374CA16FB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="5" firstSheet="5" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CVCSPSCFCorp_IPDailyNOP" r:id="rId1" sheetId="1"/>
-    <sheet name="CVCSPSCFCorp_AutomaticPayment" r:id="rId2" sheetId="2"/>
-    <sheet name="CVCSPSCFPC_AutomaticPayment" r:id="rId3" sheetId="4"/>
-    <sheet name="CVCSPSCFPS_AutomaticPayment" r:id="rId4" sheetId="3"/>
-    <sheet name="CVCSPSCFCC_AutomaticPayment" r:id="rId5" sheetId="5"/>
-    <sheet name="CVCSPSCFPS_RecDeferred" r:id="rId6" sheetId="6"/>
-    <sheet name="CVCSPSCFPC_RecDeferred" r:id="rId7" sheetId="7"/>
-    <sheet name="CVCSPSCFCorp_RecDeferred" r:id="rId8" sheetId="8"/>
-    <sheet name="CVCSPSCFCC_RecDeferred" r:id="rId9" sheetId="9"/>
-    <sheet name="CVCSPSCFPS_RecDaily" r:id="rId10" sheetId="10"/>
-    <sheet name="CVCSPSCFPC_RecDaily" r:id="rId11" sheetId="11"/>
-    <sheet name="CVCSPSCFCorp_RecDaily" r:id="rId12" sheetId="12"/>
-    <sheet name="CVCSPSCFCC_RecDaily" r:id="rId13" sheetId="13"/>
-    <sheet name="CVCSPSCFPS_IPDeferred" r:id="rId14" sheetId="14"/>
-    <sheet name="CVCSPSCFPC_IPDeferred" r:id="rId15" sheetId="15"/>
-    <sheet name="CVCSPSCFCC_IPDeferred" r:id="rId16" sheetId="16"/>
-    <sheet name="CVCSPSCFCorp_IPDeferred" r:id="rId17" sheetId="17"/>
-    <sheet name="CVCSPSCFPS_IPDailyIA" r:id="rId18" sheetId="18"/>
-    <sheet name="CVCSPSCFPC_IPDailyIA" r:id="rId19" sheetId="19"/>
-    <sheet name="CVCSPSCFCC_IPDailyIA" r:id="rId20" sheetId="20"/>
-    <sheet name="CVCSPSCFCorp_IPDailyIA" r:id="rId21" sheetId="21"/>
-    <sheet name="CVCSPSCFCC_IPDailyNOP" r:id="rId22" sheetId="22"/>
-    <sheet name="CVCSPSCFPC_IPDailyNOP" r:id="rId23" sheetId="23"/>
-    <sheet name="CVCSPSCFPS_IPDailyNOP" r:id="rId24" sheetId="24"/>
-    <sheet name="CVCSPSCFCorp_RecMonthly" r:id="rId25" sheetId="25"/>
+    <sheet name="CVCSPSCFCorp_IPDailyNOP" sheetId="1" r:id="rId1"/>
+    <sheet name="CVCSPSCFCorp_AutomaticPayment" sheetId="2" r:id="rId2"/>
+    <sheet name="CVCSPSCFPC_AutomaticPayment" sheetId="4" r:id="rId3"/>
+    <sheet name="CVCSPSCFPS_AutomaticPayment" sheetId="3" r:id="rId4"/>
+    <sheet name="CVCSPSCFCC_AutomaticPayment" sheetId="5" r:id="rId5"/>
+    <sheet name="CVCSPSCFPS_RecDeferred" sheetId="6" r:id="rId6"/>
+    <sheet name="CVCSPSCFPC_RecDeferred" sheetId="7" r:id="rId7"/>
+    <sheet name="CVCSPSCFCorp_RecDeferred" sheetId="8" r:id="rId8"/>
+    <sheet name="CVCSPSCFCC_RecDeferred" sheetId="9" r:id="rId9"/>
+    <sheet name="CVCSPSCFPS_RecDaily" sheetId="10" r:id="rId10"/>
+    <sheet name="CVCSPSCFPC_RecDaily" sheetId="11" r:id="rId11"/>
+    <sheet name="CVCSPSCFCorp_RecDaily" sheetId="12" r:id="rId12"/>
+    <sheet name="CVCSPSCFCC_RecDaily" sheetId="13" r:id="rId13"/>
+    <sheet name="CVCSPSCFPS_IPDeferred" sheetId="14" r:id="rId14"/>
+    <sheet name="CVCSPSCFPC_IPDeferred" sheetId="15" r:id="rId15"/>
+    <sheet name="CVCSPSCFCC_IPDeferred" sheetId="16" r:id="rId16"/>
+    <sheet name="CVCSPSCFCorp_IPDeferred" sheetId="17" r:id="rId17"/>
+    <sheet name="CVCSPSCFPS_IPDailyIA" sheetId="18" r:id="rId18"/>
+    <sheet name="CVCSPSCFPC_IPDailyIA" sheetId="19" r:id="rId19"/>
+    <sheet name="CVCSPSCFCC_IPDailyIA" sheetId="20" r:id="rId20"/>
+    <sheet name="CVCSPSCFCorp_IPDailyIA" sheetId="21" r:id="rId21"/>
+    <sheet name="CVCSPSCFCC_IPDailyNOP" sheetId="22" r:id="rId22"/>
+    <sheet name="CVCSPSCFPC_IPDailyNOP" sheetId="23" r:id="rId23"/>
+    <sheet name="CVCSPSCFPS_IPDailyNOP" sheetId="24" r:id="rId24"/>
+    <sheet name="CVCSPSCFCorp_RecMonthly" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="82">
   <si>
     <t>Result</t>
   </si>
@@ -138,9 +138,6 @@
   </si>
   <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>Fri Dec 26 21:37:24 IST 2025</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -163,9 +160,6 @@
 Payment Plan Type:,	Automatic Payment 
 Payment Plan Start Date:,	
 4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
-    <t>Fri Jan 02 20:14:27 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -192,12 +186,6 @@
 4. Payment Plan,1 Daily payment of $</t>
   </si>
   <si>
-    <t>Fri Jan 02 20:30:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 02 20:35:28 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -222,9 +210,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Fri Jan 02 20:40:58 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -249,9 +234,6 @@
 4. Payment Plan, Daily payments of $</t>
   </si>
   <si>
-    <t>Fri Jan 02 22:22:44 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -274,9 +256,6 @@
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
 4. Payment Plan,1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Fri Jan 02 22:29:45 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -302,9 +281,6 @@
 Payment Plan Type:,	Automatic Payment 
 Payment Plan Start Date:,	
 4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
-    <t>Fri Jan 02 22:51:23 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -334,12 +310,6 @@
 4. Payment Plan,1 Daily payment of $</t>
   </si>
   <si>
-    <t>Fri Jan 02 23:10:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Sun Jan 04 23:17:21 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -367,9 +337,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Sun Jan 04 23:21:56 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -397,9 +364,6 @@
 4. Payment Plan, Daily payments of $</t>
   </si>
   <si>
-    <t>Sun Jan 04 23:27:00 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -427,9 +391,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Sun Jan 04 23:33:55 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -457,9 +418,6 @@
 4. Payment Plan,Monthly payments of $</t>
   </si>
   <si>
-    <t>Sun Jan 04 23:39:54 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -485,9 +443,6 @@
 4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
   </si>
   <si>
-    <t>Tue Jan 06 19:40:17 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -513,12 +468,6 @@
 4. Payment Plan,1 Daily payment of $</t>
   </si>
   <si>
-    <t>Tue Jan 06 20:35:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jan 06 20:44:22 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -544,9 +493,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Tue Jan 06 21:24:34 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -572,9 +518,6 @@
 4. Payment Plan, Daily payments of $</t>
   </si>
   <si>
-    <t>Tue Jan 06 21:29:44 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -600,9 +543,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Tue Jan 06 21:33:50 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -624,9 +564,6 @@
 Payment Plan Type:,	Automatic Payment 
 Payment Plan Start Date:,	
 4. Payment Plan, Amount due will be paid 3 calendar days before the Due Date</t>
-  </si>
-  <si>
-    <t>Tue Jan 06 22:45:44 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -654,12 +591,6 @@
 4. Payment Plan,1 Daily payment of $</t>
   </si>
   <si>
-    <t>Tue Jan 06 22:56:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Jan 06 23:03:07 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -685,9 +616,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Tue Jan 06 23:08:30 IST 2026</t>
-  </si>
-  <si>
     <t>Scheduled Payment--View the Information,
 Remittance ID: 6210-402999,
 1. Review bill to pay,
@@ -710,9 +638,6 @@
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
 4. Payment Plan, Daily payments of $</t>
-  </si>
-  <si>
-    <t>Tue Jan 06 23:12:31 IST 2026</t>
   </si>
   <si>
     <t>Scheduled Payment--View the Information,
@@ -740,12 +665,6 @@
 4. Payment Plan,1 Deferred payment of $</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Tue Jan 06 23:16:45 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 03 20:38:47 IST 2026</t>
   </si>
   <si>
@@ -764,159 +683,6 @@
     <t>Fri Jul 03 20:42:59 IST 2026</t>
   </si>
   <si>
-    <t>Fri Jul 03 20:43:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:45:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:46:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:47:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:48:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:50:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:52:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:55:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:57:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:58:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 20:59:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:00:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:01:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:02:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:03:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:05:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:06:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:07:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:08:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:09:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:11:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:12:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:13:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:14:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:15:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:16:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:17:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:18:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:19:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:21:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:21:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:22:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:24:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:26:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:28:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:30:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:32:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:33:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:34:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:36:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:37:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:38:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:39:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:40:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:41:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:42:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:43:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:45:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:46:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:47:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 21:48:21 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 03 21:49:26 IST 2026</t>
   </si>
   <si>
@@ -936,6 +702,298 @@
   </si>
   <si>
     <t>Fri Jul 03 21:53:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 19:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 19:50:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 20:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 20:29:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 20:36:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 20:39:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+Company Name:,	Vaddahun Corp,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Business Tax ID:,	999999999,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8903,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,Business Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Monthly,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,Monthly payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 20:43:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 21:11:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 21:16:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 21:19:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Installment Plan,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 21:24:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Daily,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 21:26:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Scheduled Payment--View the Information,_x000D_
+Remittance ID: 6210-402999,_x000D_
+1. Review bill to pay,_x000D_
+Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	_x000D_
+AutoABPDemoBBGSCF6210,	 EST, 	_x000D_
+UDF1:,	udf data 1,_x000D_
+UDF2:,	udf data 2,_x000D_
+UDF3:,	udf3,_x000D_
+UDF4:,	udf data4,_x000D_
+2. Payment Method,_x000D_
+First Name:,	DULIP,_x000D_
+Last Name:,	EKANAYAKE,_x000D_
+Routing Number:,	****2691,_x000D_
+Account Number:,	****8904,_x000D_
+Billing Address:,	708 36TH AVE NW,,_x000D_
+Hickory, New York NY, 28601,_x000D_
+Country:,	UNITED STATES,_x000D_
+Account Type:,	Personal Checking,_x000D_
+3. Payment Plan Information,_x000D_
+Payment Plan Type:,	Recurring,_x000D_
+Payment Plan Duration:,	Deferred,_x000D_
+Payment Plan Start Date:,	_x000D_
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	_x000D_
+Total Convenience Fees Paid:,	_x000D_
+Total Paid under this plan:</t>
+  </si>
+  <si>
+    <t>Wed Jul 29 21:41:06 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1004,46 +1062,46 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="164" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="2" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1060,10 +1118,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1098,7 +1156,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1133,7 +1191,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1227,21 +1285,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1258,7 +1316,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1310,14 +1368,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1325,7 +1383,7 @@
     <col min="11" max="11" customWidth="true" width="30.26953125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1375,12 +1433,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1406,11 +1464,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1418,47 +1476,20 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1466,14 +1497,14 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B5A2A1-86A0-48D6-8551-F95C124FFD93}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="26.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,12 +1554,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1554,11 +1585,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1589,7 +1620,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1597,25 +1628,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12333DF-E1A4-40DF-9EB9-E0927AF8848C}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1665,12 +1696,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1696,11 +1727,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1708,57 +1739,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E13466-8780-4BE7-977B-AE4E7A3ED92C}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1808,12 +1814,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1839,11 +1845,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -1851,59 +1857,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4BB029-1171-41FA-A648-8FA4436E795E}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="34.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1953,12 +1932,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1984,11 +1963,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2019,7 +1998,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan, Daily payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan, Daily payments of $10.00 starting on 07/30/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2027,18 +2006,18 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972198C4-EADB-4F49-BACE-22D2E17BA962}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2047,7 +2026,7 @@
     <col min="16" max="16" customWidth="true" width="17.1796875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2097,12 +2076,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2128,11 +2107,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2164,7 +2143,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2172,25 +2151,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A72D8C-277B-4875-8E77-2139760B0ECA}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.26953125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2240,12 +2219,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2271,11 +2250,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2283,57 +2262,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EC6F33-051D-49DA-A956-296219E0BF32}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2383,12 +2337,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2414,11 +2368,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2449,7 +2403,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2457,25 +2411,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66606A84-4AB3-491D-9D66-F6130A959AD3}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="25.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2525,12 +2479,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2556,11 +2510,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2568,59 +2522,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{052F609E-8671-42DF-A52E-E0D9BD0CD203}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2670,12 +2597,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2701,11 +2628,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2737,7 +2664,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -2745,25 +2672,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3600924-F2FB-45A8-BED7-C929CC9ED1B0}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2813,12 +2740,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2844,11 +2771,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -2856,57 +2783,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE468B6-189E-4673-8A1F-0ED1617BC5B6}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2956,12 +2858,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2987,11 +2889,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3010,19 +2912,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1882DF2-9DD6-4023-94DD-D03DA9278EDA}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3072,12 +2974,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3103,11 +3005,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3138,7 +3040,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3146,25 +3048,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DE1098-DCCB-4F87-87C7-D2AB1CA20D07}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.36328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3214,12 +3116,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3245,11 +3147,11 @@
         <v>24</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3257,59 +3159,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAC6D03-D5E5-4638-94D0-65ECE68C7A9E}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.08984375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3359,12 +3234,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3390,11 +3265,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3425,7 +3300,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3433,25 +3308,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091E6D05-9B7E-4C82-8712-7C58E6433EF7}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3501,12 +3376,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3532,11 +3407,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3544,57 +3419,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Installment Plan,
-Payment Plan Duration:,	Daily,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39AC360F-0C63-4638-A4B3-246CDDD4C83D}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="29.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3644,12 +3494,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3675,11 +3525,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3711,7 +3561,7 @@
 Payment Plan Type:,	Installment Plan,
 Payment Plan Duration:,	Daily,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Daily payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Daily payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -3719,25 +3569,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7AAE7D8-8383-49E4-B847-6D1C69A1CC13}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.1796875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3787,12 +3637,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3818,11 +3668,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3830,52 +3680,25 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" starting on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Monthly,
-Payment Plan Start Date:,	
-4. Payment Plan,Monthly payments of $10.00 starting on 01/07/2026,A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Monthly payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Monthly payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A1E8BE-D33F-4968-8266-BE3EF6209F01}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3885,7 +3708,7 @@
     <col min="11" max="11" customWidth="true" width="22.6328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3935,12 +3758,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3966,11 +3789,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -3989,19 +3812,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EBDAF58-F67E-4B6A-98CB-1AEB684984F2}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="19.6328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4051,12 +3874,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4082,11 +3905,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4105,19 +3928,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146453A-566F-4243-8B47-2F88A434AC05}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="30.54296875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4167,12 +3990,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4198,11 +4021,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4221,19 +4044,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD627C4-0639-4F31-B018-C711C491A530}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="17.90625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4283,12 +4106,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4314,11 +4137,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4350,7 +4173,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4358,25 +4181,25 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CCCC01-8D91-4DD2-9F92-02AFB7FF39EF}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="23.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4426,12 +4249,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4457,11 +4280,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4469,57 +4292,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Personal Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC15A6F-3592-43D9-BD24-8AE9729D36B7}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.81640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4569,12 +4367,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4600,11 +4398,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4612,59 +4410,32 @@
       <c r="N2" s="8">
         <v>2</v>
       </c>
-      <c r="O2" s="9" t="str">
-        <f ca="1">K2&amp;TEXT(M2,"0.00")&amp;" on "&amp;L2&amp;","&amp;P2</f>
-        <v>Scheduled Payment--View the Information,
-Remittance ID: 6210-402999,
-1. Review bill to pay,
-Pending Bills,	Due Date,	Date Submitted,	Date Modified,	Amount Due,	Amount to Pay,	
-AutoABPDemoBBGSCF6210,	 EST, 	
-UDF1:,	udf data 1,
-UDF2:,	udf data 2,
-UDF3:,	udf3,
-UDF4:,	udf data4,
-2. Payment Method,
-Company Name:,	Vaddahun Corp,
-First Name:,	DULIP,
-Last Name:,	EKANAYAKE,
-Business Tax ID:,	999999999,
-Routing Number:,	****2691,
-Account Number:,	****5489,
-Billing Address:,	708 36TH AVE NW,,
-Hickory, New York NY, 28601,
-Country:,	UNITED STATES,
-Account Type:,	Business Checking,
-3. Payment Plan Information,
-Payment Plan Type:,	Recurring,
-Payment Plan Duration:,	Deferred,
-Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:</v>
+      <c r="O2" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="P2" s="10" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F2B77E-010E-4115-88A3-B1B1A5BAFCF1}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="28.54296875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4714,12 +4485,12 @@
         <v>13</v>
       </c>
     </row>
-    <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4745,11 +4516,11 @@
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>01/07/2026</v>
+        <v>07/30/2026</v>
       </c>
       <c r="M2" s="7">
         <v>10</v>
@@ -4780,7 +4551,7 @@
 Payment Plan Type:,	Recurring,
 Payment Plan Duration:,	Deferred,
 Payment Plan Start Date:,	
-4. Payment Plan,1 Deferred payment of $10.00 on 01/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+4. Payment Plan,1 Deferred payment of $10.00 on 07/30/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -4788,12 +4559,12 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(N2,"0.00")&amp;" starting on "&amp;L2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 01/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/30/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>